--- a/data/trans_bre/P7_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P7_R-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 8,68</t>
+          <t>-4,32; 7,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,42; 22,96</t>
+          <t>6,88; 23,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 17,61</t>
+          <t>2,14; 17,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,59; 17,27</t>
+          <t>2,29; 16,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-24,57; 66,27</t>
+          <t>-22,9; 60,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,9; 115,26</t>
+          <t>24,0; 111,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,4; 85,62</t>
+          <t>7,04; 83,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,6; 89,43</t>
+          <t>8,0; 82,61</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,35; 19,83</t>
+          <t>9,39; 19,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,92; 19,37</t>
+          <t>8,13; 19,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,59; 12,7</t>
+          <t>3,12; 12,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 7,88</t>
+          <t>-0,97; 8,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>45,96; 130,57</t>
+          <t>47,75; 135,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,52; 131,95</t>
+          <t>39,13; 129,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,58; 101,28</t>
+          <t>18,24; 105,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 62,02</t>
+          <t>-5,69; 65,34</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,27; 24,53</t>
+          <t>11,71; 24,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 14,1</t>
+          <t>1,2; 13,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 9,17</t>
+          <t>-1,9; 9,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 8,43</t>
+          <t>-2,29; 8,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>60,96; 216,18</t>
+          <t>62,55; 211,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,94; 109,09</t>
+          <t>4,15; 111,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-14,89; 83,2</t>
+          <t>-12,67; 93,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,51; 50,95</t>
+          <t>-10,06; 52,88</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,5; 21,67</t>
+          <t>10,04; 21,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,16; 20,82</t>
+          <t>8,05; 20,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,86; 18,43</t>
+          <t>5,78; 18,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 8,93</t>
+          <t>-8,17; 9,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>74,12; 248,47</t>
+          <t>75,45; 253,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,72; 126,76</t>
+          <t>32,43; 125,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,33; 118,59</t>
+          <t>24,78; 115,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,79; 50,71</t>
+          <t>-33,21; 52,7</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,59; 23,38</t>
+          <t>5,42; 23,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,66; 22,75</t>
+          <t>6,37; 22,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 14,15</t>
+          <t>-2,28; 13,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 10,46</t>
+          <t>-3,46; 10,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,16; 137,17</t>
+          <t>19,85; 134,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,49; 179,66</t>
+          <t>29,14; 190,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 86,36</t>
+          <t>-8,74; 83,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-17,56; 120,68</t>
+          <t>-26,43; 125,21</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,61; 26,89</t>
+          <t>12,66; 26,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,31; 14,62</t>
+          <t>0,67; 15,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 14,01</t>
+          <t>-0,32; 13,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 10,42</t>
+          <t>-0,96; 10,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>78,91; 269,96</t>
+          <t>73,97; 260,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,96; 93,36</t>
+          <t>2,35; 100,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 98,8</t>
+          <t>-3,14; 98,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 51,9</t>
+          <t>-3,48; 55,19</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,15; 19,33</t>
+          <t>9,69; 18,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,15; 12,55</t>
+          <t>4,19; 12,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,71; 13,88</t>
+          <t>5,56; 13,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 10,36</t>
+          <t>-7,07; 10,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>62,43; 162,36</t>
+          <t>59,32; 153,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,5; 98,15</t>
+          <t>24,59; 95,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,61; 114,13</t>
+          <t>34,12; 112,86</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-42,08; 73,27</t>
+          <t>-41,5; 73,57</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,56; 11,87</t>
+          <t>3,64; 12,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,13; 9,79</t>
+          <t>1,94; 9,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,64; 12,14</t>
+          <t>4,69; 11,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,26; 20,55</t>
+          <t>6,85; 20,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,68; 75,98</t>
+          <t>18,49; 78,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,94; 88,87</t>
+          <t>11,92; 88,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,81; 114,79</t>
+          <t>33,92; 112,95</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>32,37; 317,64</t>
+          <t>35,78; 330,91</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10,76; 14,89</t>
+          <t>10,9; 15,08</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,95; 11,99</t>
+          <t>8,0; 12,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,03; 9,93</t>
+          <t>6,3; 10,25</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,75; 8,96</t>
+          <t>1,78; 9,04</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>64,22; 100,58</t>
+          <t>65,49; 101,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>44,52; 76,17</t>
+          <t>45,47; 76,24</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36,13; 67,32</t>
+          <t>38,96; 69,69</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11,21; 62,96</t>
+          <t>10,39; 64,82</t>
         </is>
       </c>
     </row>
